--- a/docs/lem/files/xslope_gsat_piezo.xlsx
+++ b/docs/lem/files/xslope_gsat_piezo.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="318">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -992,6 +992,167 @@
   </si>
   <si>
     <t>auto</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c/p)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(d)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>sat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>q</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3243,7 +3404,7 @@
         <v>270</v>
       </c>
       <c r="H2" s="40" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="I2" s="40" t="s">
         <v>253</v>
@@ -5722,7 +5883,7 @@
         <v>111</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>112</v>
+        <v>316</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>113</v>
@@ -5791,22 +5952,22 @@
         <v>133</v>
       </c>
       <c r="AA10" s="46" t="s">
-        <v>134</v>
+        <v>311</v>
       </c>
       <c r="AB10" s="46" t="s">
-        <v>135</v>
+        <v>312</v>
       </c>
       <c r="AC10" s="47" t="s">
         <v>136</v>
       </c>
       <c r="AD10" s="46" t="s">
-        <v>137</v>
+        <v>313</v>
       </c>
       <c r="AE10" s="46" t="s">
-        <v>138</v>
+        <v>314</v>
       </c>
       <c r="AF10" s="47" t="s">
-        <v>139</v>
+        <v>315</v>
       </c>
       <c r="AG10" s="23" t="s">
         <v>140</v>
